--- a/data/Lookup_Tables/impuestos.XLSX
+++ b/data/Lookup_Tables/impuestos.XLSX
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24334"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11003"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://upcomillas-my.sharepoint.com/personal/mmcamacho_comillas_edu/Documents/Archivos de chat de Microsoft Teams/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/beatrizreglero/Desktop/TFG/TFG_Entregas/data/Lookup_Tables/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{0D0DB7C4-A640-4C61-B39C-DEFB58146115}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7B2C658-9F64-1644-BD44-715EDCA0E2F8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="22695" windowHeight="14476" xr2:uid="{CDCC7379-CBD2-450E-B9A0-A5951CE9A962}"/>
+    <workbookView xWindow="0" yWindow="500" windowWidth="22700" windowHeight="14480" xr2:uid="{CDCC7379-CBD2-450E-B9A0-A5951CE9A962}"/>
   </bookViews>
   <sheets>
     <sheet name="impuestos" sheetId="1" r:id="rId1"/>
@@ -29,9 +29,6 @@
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
     </ext>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
   </extLst>
 </workbook>
 </file>
@@ -85,10 +82,17 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -116,7 +120,7 @@
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -135,9 +139,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Tema de Office">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - Tema de 2022">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -175,7 +179,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -281,7 +285,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -423,7 +427,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -432,9 +436,9 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5E85AC7B-1F0F-4B01-8E04-D54342B853B5}">
   <dimension ref="A1:C9"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -445,7 +449,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A3" t="s">
         <v>3</v>
       </c>
@@ -456,18 +460,18 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A4" t="s">
         <v>6</v>
       </c>
       <c r="B4" s="1">
-        <v>5511</v>
+        <v>5.5110000000000001</v>
       </c>
       <c r="C4" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A5" t="s">
         <v>8</v>
       </c>
@@ -478,7 +482,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A6" t="s">
         <v>10</v>
       </c>
@@ -486,7 +490,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A7" t="s">
         <v>11</v>
       </c>
@@ -494,7 +498,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A8" t="s">
         <v>12</v>
       </c>
@@ -502,7 +506,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A9" t="s">
         <v>13</v>
       </c>
@@ -516,6 +520,21 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x0101008CC35A7A26A4324F8F38BD84F25AF9C1" ma:contentTypeVersion="7" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="b819923d2297222e9ee10f9e0fee1a03">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="b193dfaa-deae-48b4-a85f-1fcd6ead3755" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="db138671d8e145de4e330d26d84748c1" ns2:_="">
     <xsd:import namespace="b193dfaa-deae-48b4-a85f-1fcd6ead3755"/>
@@ -677,29 +696,37 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{95BAA432-9D40-4818-A570-37A8F8305084}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D0782A6-245A-49A1-971E-2E02E4C64B60}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{885561D9-7113-495E-84FA-4A396678CEB1}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{885561D9-7113-495E-84FA-4A396678CEB1}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8D0782A6-245A-49A1-971E-2E02E4C64B60}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{95BAA432-9D40-4818-A570-37A8F8305084}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="b193dfaa-deae-48b4-a85f-1fcd6ead3755"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>